--- a/report_forms/018_smart_sensor_calibration_report_form--report_forms.xlsx
+++ b/report_forms/018_smart_sensor_calibration_report_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Report Details</t>
+          <t>Calibration Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sensor Calibration Data</t>
+          <t>Calibration Status</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Calibration Comments</t>
+          <t>Sensor Type</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,20 +686,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Calibration Notes</t>
+          <t>Equipment Serial Number</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Report Date</t>
+          <t>Calibration Number</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Submission Status</t>
+          <t>Sensor Calibration Frequency</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sensor Type</t>
+          <t>Report Number</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Equipment Serial Number</t>
+          <t>Sensor Serial Number</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Calibration Number</t>
+          <t>Sensor ID</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sensor Calibration Frequency</t>
+          <t>Smart Sensor Calibration Report Form Page 14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,13 +847,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Report Number</t>
+          <t>Sensor Data</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serial Number</t>
+          <t>Smart Sensor Calibration Report Form Page 16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sensor_type</t>
+          <t>Calibration Location</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,172 +916,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>equipment_serial_number</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>smart_sensor_calibration_report_form_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>calibration_number</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>smart_sensor_calibration_report_form_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>sensor_calibration_frequency</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>smart_sensor_calibration_report_form_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>report_number</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>smart_sensor_calibration_report_form_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>sensor_serial_number</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>smart_sensor_calibration_report_form_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>sensor_id</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>smart_sensor_calibration_report_form_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>sensor_frequency</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>smart_sensor_calibration_report_form_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>sensor_data</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Draft</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1250,114 +1089,63 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>published</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>smart_sensor_calibration_report_form_page_6_choices</t>
+          <t>smart_sensor_calibration_report_form_page_7_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>smart_sensor_calibration_report_form_page_10_choices</t>
+          <t>smart_sensor_calibration_report_form_page_7_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>smart_sensor_calibration_report_form_page_10_choices</t>
+          <t>smart_sensor_calibration_report_form_page_7_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>published</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Published</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>smart_sensor_calibration_report_form_page_11_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>smart_sensor_calibration_report_form_page_11_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>smart_sensor_calibration_report_form_page_11_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
